--- a/assets_output/06_bivariate_DVs_by_characteristics.xlsx
+++ b/assets_output/06_bivariate_DVs_by_characteristics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="354">
   <si>
     <t>Cross-tabulation of entry point into bahsa services by gender (n)</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>pl_outcome</t>
+  </si>
+  <si>
+    <t>Insecure outcome (external)</t>
   </si>
   <si>
     <t>Internal move: backwards</t>
@@ -2895,7 +2898,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B97">
         <v>168</v>
@@ -2915,7 +2918,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B98">
         <v>225</v>
@@ -2935,7 +2938,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B99">
         <v>458</v>
@@ -2955,7 +2958,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B100">
         <v>283</v>
@@ -3015,7 +3018,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3077,7 +3080,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B108">
         <v>9.9</v>
@@ -3097,7 +3100,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B109">
         <v>13.2</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B110">
         <v>27</v>
@@ -3137,7 +3140,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B111">
         <v>16.7</v>
@@ -3197,7 +3200,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3382,7 +3385,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3567,7 +3570,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3674,7 +3677,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3781,7 +3784,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3888,7 +3891,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3995,7 +3998,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4068,7 +4071,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4141,7 +4144,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4214,7 +4217,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4287,7 +4290,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4357,7 +4360,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4427,7 +4430,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4483,7 +4486,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B211">
         <v>485</v>
@@ -4500,7 +4503,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B212">
         <v>510</v>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B213">
         <v>1182</v>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B214">
         <v>977</v>
@@ -4585,7 +4588,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4641,7 +4644,7 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B222">
         <v>10.5</v>
@@ -4658,7 +4661,7 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B223">
         <v>11</v>
@@ -4675,7 +4678,7 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B224">
         <v>25.5</v>
@@ -4692,7 +4695,7 @@
     </row>
     <row r="225" spans="1:10">
       <c r="A225" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B225">
         <v>21.1</v>
@@ -4743,7 +4746,7 @@
     </row>
     <row r="229" spans="1:10">
       <c r="A229" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -4754,25 +4757,25 @@
         <v>7</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>5</v>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="241" spans="1:10">
       <c r="A241" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -5059,25 +5062,25 @@
         <v>7</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>5</v>
@@ -5353,7 +5356,7 @@
     </row>
     <row r="253" spans="1:10">
       <c r="A253" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -5361,25 +5364,25 @@
         <v>16</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>5</v>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -5540,25 +5543,25 @@
         <v>16</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>5</v>
@@ -5711,7 +5714,7 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -5719,25 +5722,25 @@
         <v>23</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>5</v>
@@ -5890,7 +5893,7 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -5898,25 +5901,25 @@
         <v>23</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>5</v>
@@ -6069,7 +6072,7 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -6077,25 +6080,25 @@
         <v>26</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>5</v>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -6198,25 +6201,25 @@
         <v>26</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>5</v>
@@ -6311,7 +6314,7 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -6319,25 +6322,25 @@
         <v>29</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>5</v>
@@ -6432,7 +6435,7 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -6440,25 +6443,25 @@
         <v>29</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>5</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -6561,25 +6564,25 @@
         <v>32</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>5</v>
@@ -6671,7 +6674,7 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -6679,25 +6682,25 @@
         <v>32</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>5</v>
@@ -6783,7 +6786,7 @@
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -6791,25 +6794,25 @@
         <v>37</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>5</v>
@@ -6875,7 +6878,7 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -6904,7 +6907,7 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B326">
         <v>1</v>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B327">
         <v>1</v>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -7057,25 +7060,25 @@
         <v>37</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>5</v>
@@ -7141,7 +7144,7 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -7170,7 +7173,7 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B337">
         <v>50</v>
@@ -7199,7 +7202,7 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B338">
         <v>50</v>
@@ -7228,7 +7231,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -7315,7 +7318,7 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -7500,7 +7503,7 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -7685,7 +7688,7 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -7792,7 +7795,7 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7899,7 +7902,7 @@
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -8006,7 +8009,7 @@
     </row>
     <row r="391" spans="1:5">
       <c r="A391" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -8113,7 +8116,7 @@
     </row>
     <row r="399" spans="1:5">
       <c r="A399" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -8186,7 +8189,7 @@
     </row>
     <row r="405" spans="1:5">
       <c r="A405" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -8259,7 +8262,7 @@
     </row>
     <row r="411" spans="1:5">
       <c r="A411" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -8332,7 +8335,7 @@
     </row>
     <row r="417" spans="1:5">
       <c r="A417" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -8405,7 +8408,7 @@
     </row>
     <row r="423" spans="1:5">
       <c r="A423" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -8478,7 +8481,7 @@
     </row>
     <row r="429" spans="1:5">
       <c r="A429" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -8551,7 +8554,7 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -8607,7 +8610,7 @@
     </row>
     <row r="439" spans="1:5">
       <c r="A439" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B439">
         <v>468</v>
@@ -8624,7 +8627,7 @@
     </row>
     <row r="440" spans="1:5">
       <c r="A440" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B440">
         <v>507</v>
@@ -8641,7 +8644,7 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B441">
         <v>1192</v>
@@ -8658,7 +8661,7 @@
     </row>
     <row r="442" spans="1:5">
       <c r="A442" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B442">
         <v>899</v>
@@ -8709,7 +8712,7 @@
     </row>
     <row r="446" spans="1:5">
       <c r="A446" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -8765,7 +8768,7 @@
     </row>
     <row r="450" spans="1:5">
       <c r="A450" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B450">
         <v>10.2</v>
@@ -8782,7 +8785,7 @@
     </row>
     <row r="451" spans="1:5">
       <c r="A451" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B451">
         <v>11.1</v>
@@ -8799,7 +8802,7 @@
     </row>
     <row r="452" spans="1:5">
       <c r="A452" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B452">
         <v>26</v>
@@ -8816,7 +8819,7 @@
     </row>
     <row r="453" spans="1:5">
       <c r="A453" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B453">
         <v>19.6</v>
@@ -8867,7 +8870,7 @@
     </row>
     <row r="457" spans="1:5">
       <c r="A457" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -9022,7 +9025,7 @@
     </row>
     <row r="469" spans="1:5">
       <c r="A469" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -9177,7 +9180,7 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -9266,7 +9269,7 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -9355,7 +9358,7 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -9444,7 +9447,7 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9533,7 +9536,7 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9594,7 +9597,7 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9655,7 +9658,7 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9716,7 +9719,7 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9777,7 +9780,7 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9838,7 +9841,7 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9899,7 +9902,7 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9946,7 +9949,7 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B553">
         <v>373</v>
@@ -9960,7 +9963,7 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B554">
         <v>503</v>
@@ -9974,7 +9977,7 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B555">
         <v>1210</v>
@@ -9988,7 +9991,7 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B556">
         <v>799</v>
@@ -10030,7 +10033,7 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -10077,7 +10080,7 @@
     </row>
     <row r="564" spans="1:5">
       <c r="A564" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B564">
         <v>8.699999999999999</v>
@@ -10091,7 +10094,7 @@
     </row>
     <row r="565" spans="1:5">
       <c r="A565" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B565">
         <v>11.8</v>
@@ -10105,7 +10108,7 @@
     </row>
     <row r="566" spans="1:5">
       <c r="A566" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B566">
         <v>28.3</v>
@@ -10119,7 +10122,7 @@
     </row>
     <row r="567" spans="1:5">
       <c r="A567" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B567">
         <v>18.7</v>
@@ -10161,7 +10164,7 @@
     </row>
     <row r="571" spans="1:5">
       <c r="A571" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -10316,7 +10319,7 @@
     </row>
     <row r="583" spans="1:5">
       <c r="A583" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -10471,7 +10474,7 @@
     </row>
     <row r="595" spans="1:5">
       <c r="A595" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -10560,7 +10563,7 @@
     </row>
     <row r="603" spans="1:5">
       <c r="A603" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -10649,7 +10652,7 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10738,7 +10741,7 @@
     </row>
     <row r="619" spans="1:4">
       <c r="A619" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -10827,7 +10830,7 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -10888,7 +10891,7 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -10949,7 +10952,7 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -11010,7 +11013,7 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -11071,7 +11074,7 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -11132,7 +11135,7 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -11193,7 +11196,7 @@
     </row>
     <row r="663" spans="1:4">
       <c r="A663" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -11240,7 +11243,7 @@
     </row>
     <row r="667" spans="1:4">
       <c r="A667" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B667">
         <v>310</v>
@@ -11254,7 +11257,7 @@
     </row>
     <row r="668" spans="1:4">
       <c r="A668" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B668">
         <v>365</v>
@@ -11268,7 +11271,7 @@
     </row>
     <row r="669" spans="1:4">
       <c r="A669" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B669">
         <v>883</v>
@@ -11282,7 +11285,7 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B670">
         <v>608</v>
@@ -11324,7 +11327,7 @@
     </row>
     <row r="674" spans="1:5">
       <c r="A674" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -11371,7 +11374,7 @@
     </row>
     <row r="678" spans="1:5">
       <c r="A678" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B678">
         <v>9.6</v>
@@ -11385,7 +11388,7 @@
     </row>
     <row r="679" spans="1:5">
       <c r="A679" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B679">
         <v>11.3</v>
@@ -11399,7 +11402,7 @@
     </row>
     <row r="680" spans="1:5">
       <c r="A680" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B680">
         <v>27.4</v>
@@ -11413,7 +11416,7 @@
     </row>
     <row r="681" spans="1:5">
       <c r="A681" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B681">
         <v>18.9</v>
@@ -11455,7 +11458,7 @@
     </row>
     <row r="685" spans="1:5">
       <c r="A685" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -11610,7 +11613,7 @@
     </row>
     <row r="697" spans="1:5">
       <c r="A697" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="698" spans="1:5">
@@ -11765,7 +11768,7 @@
     </row>
     <row r="709" spans="1:5">
       <c r="A709" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="710" spans="1:5">
@@ -11854,7 +11857,7 @@
     </row>
     <row r="717" spans="1:5">
       <c r="A717" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="718" spans="1:5">
@@ -11943,7 +11946,7 @@
     </row>
     <row r="725" spans="1:4">
       <c r="A725" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -12032,7 +12035,7 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -12121,7 +12124,7 @@
     </row>
     <row r="741" spans="1:4">
       <c r="A741" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -12182,7 +12185,7 @@
     </row>
     <row r="747" spans="1:4">
       <c r="A747" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -12243,7 +12246,7 @@
     </row>
     <row r="753" spans="1:4">
       <c r="A753" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -12304,7 +12307,7 @@
     </row>
     <row r="759" spans="1:4">
       <c r="A759" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="760" spans="1:4">
@@ -12365,7 +12368,7 @@
     </row>
     <row r="765" spans="1:4">
       <c r="A765" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="766" spans="1:4">
@@ -12426,7 +12429,7 @@
     </row>
     <row r="771" spans="1:4">
       <c r="A771" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="772" spans="1:4">
@@ -12487,7 +12490,7 @@
     </row>
     <row r="777" spans="1:4">
       <c r="A777" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="778" spans="1:4">
@@ -12534,7 +12537,7 @@
     </row>
     <row r="781" spans="1:4">
       <c r="A781" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B781">
         <v>131</v>
@@ -12548,7 +12551,7 @@
     </row>
     <row r="782" spans="1:4">
       <c r="A782" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B782">
         <v>129</v>
@@ -12562,7 +12565,7 @@
     </row>
     <row r="783" spans="1:4">
       <c r="A783" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B783">
         <v>380</v>
@@ -12576,7 +12579,7 @@
     </row>
     <row r="784" spans="1:4">
       <c r="A784" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B784">
         <v>217</v>
@@ -12618,7 +12621,7 @@
     </row>
     <row r="788" spans="1:5">
       <c r="A788" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="789" spans="1:5">
@@ -12665,7 +12668,7 @@
     </row>
     <row r="792" spans="1:5">
       <c r="A792" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B792">
         <v>9.5</v>
@@ -12679,7 +12682,7 @@
     </row>
     <row r="793" spans="1:5">
       <c r="A793" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B793">
         <v>9.300000000000001</v>
@@ -12693,7 +12696,7 @@
     </row>
     <row r="794" spans="1:5">
       <c r="A794" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B794">
         <v>27.4</v>
@@ -12707,7 +12710,7 @@
     </row>
     <row r="795" spans="1:5">
       <c r="A795" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B795">
         <v>15.7</v>
@@ -12749,7 +12752,7 @@
     </row>
     <row r="799" spans="1:5">
       <c r="A799" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="800" spans="1:5">
@@ -12904,7 +12907,7 @@
     </row>
     <row r="811" spans="1:5">
       <c r="A811" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="812" spans="1:5">
@@ -13059,7 +13062,7 @@
     </row>
     <row r="823" spans="1:5">
       <c r="A823" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="824" spans="1:5">
@@ -13148,7 +13151,7 @@
     </row>
     <row r="831" spans="1:5">
       <c r="A831" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="832" spans="1:5">
@@ -13237,7 +13240,7 @@
     </row>
     <row r="839" spans="1:4">
       <c r="A839" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="840" spans="1:4">
@@ -13326,7 +13329,7 @@
     </row>
     <row r="847" spans="1:4">
       <c r="A847" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="848" spans="1:4">
@@ -13415,7 +13418,7 @@
     </row>
     <row r="855" spans="1:4">
       <c r="A855" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="856" spans="1:4">
@@ -13476,7 +13479,7 @@
     </row>
     <row r="861" spans="1:4">
       <c r="A861" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="862" spans="1:4">
@@ -13537,7 +13540,7 @@
     </row>
     <row r="867" spans="1:4">
       <c r="A867" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="868" spans="1:4">
@@ -13598,7 +13601,7 @@
     </row>
     <row r="873" spans="1:4">
       <c r="A873" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="874" spans="1:4">
@@ -13659,7 +13662,7 @@
     </row>
     <row r="879" spans="1:4">
       <c r="A879" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="880" spans="1:4">
@@ -13720,7 +13723,7 @@
     </row>
     <row r="885" spans="1:4">
       <c r="A885" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="886" spans="1:4">
@@ -13781,7 +13784,7 @@
     </row>
     <row r="891" spans="1:4">
       <c r="A891" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="892" spans="1:4">
@@ -13828,7 +13831,7 @@
     </row>
     <row r="895" spans="1:4">
       <c r="A895" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B895">
         <v>208</v>
@@ -13842,7 +13845,7 @@
     </row>
     <row r="896" spans="1:4">
       <c r="A896" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B896">
         <v>164</v>
@@ -13856,7 +13859,7 @@
     </row>
     <row r="897" spans="1:4">
       <c r="A897" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B897">
         <v>651</v>
@@ -13870,7 +13873,7 @@
     </row>
     <row r="898" spans="1:4">
       <c r="A898" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B898">
         <v>180</v>
@@ -13912,7 +13915,7 @@
     </row>
     <row r="902" spans="1:4">
       <c r="A902" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="903" spans="1:4">
@@ -13959,7 +13962,7 @@
     </row>
     <row r="906" spans="1:4">
       <c r="A906" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B906">
         <v>10.1</v>
@@ -13973,7 +13976,7 @@
     </row>
     <row r="907" spans="1:4">
       <c r="A907" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B907">
         <v>8</v>
@@ -13987,7 +13990,7 @@
     </row>
     <row r="908" spans="1:4">
       <c r="A908" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B908">
         <v>31.7</v>
@@ -14001,7 +14004,7 @@
     </row>
     <row r="909" spans="1:4">
       <c r="A909" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B909">
         <v>8.800000000000001</v>
@@ -14043,7 +14046,7 @@
     </row>
     <row r="913" spans="1:5">
       <c r="A913" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="914" spans="1:5">
@@ -14198,7 +14201,7 @@
     </row>
     <row r="925" spans="1:5">
       <c r="A925" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="926" spans="1:5">
@@ -14353,7 +14356,7 @@
     </row>
     <row r="937" spans="1:5">
       <c r="A937" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="938" spans="1:5">
@@ -14442,7 +14445,7 @@
     </row>
     <row r="945" spans="1:4">
       <c r="A945" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="946" spans="1:4">
@@ -14531,7 +14534,7 @@
     </row>
     <row r="953" spans="1:4">
       <c r="A953" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -14620,7 +14623,7 @@
     </row>
     <row r="961" spans="1:4">
       <c r="A961" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="962" spans="1:4">
@@ -14709,7 +14712,7 @@
     </row>
     <row r="969" spans="1:4">
       <c r="A969" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -14770,7 +14773,7 @@
     </row>
     <row r="975" spans="1:4">
       <c r="A975" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="976" spans="1:4">
@@ -14831,7 +14834,7 @@
     </row>
     <row r="981" spans="1:4">
       <c r="A981" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="982" spans="1:4">
@@ -14892,7 +14895,7 @@
     </row>
     <row r="987" spans="1:4">
       <c r="A987" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="988" spans="1:4">
@@ -14953,7 +14956,7 @@
     </row>
     <row r="993" spans="1:4">
       <c r="A993" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="994" spans="1:4">
@@ -15014,7 +15017,7 @@
     </row>
     <row r="999" spans="1:4">
       <c r="A999" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1000" spans="1:4">
@@ -15075,7 +15078,7 @@
     </row>
     <row r="1005" spans="1:4">
       <c r="A1005" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1006" spans="1:4">
@@ -15122,7 +15125,7 @@
     </row>
     <row r="1009" spans="1:4">
       <c r="A1009" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1009">
         <v>191</v>
@@ -15136,7 +15139,7 @@
     </row>
     <row r="1010" spans="1:4">
       <c r="A1010" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1010">
         <v>179</v>
@@ -15150,7 +15153,7 @@
     </row>
     <row r="1011" spans="1:4">
       <c r="A1011" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1011">
         <v>654</v>
@@ -15164,7 +15167,7 @@
     </row>
     <row r="1012" spans="1:4">
       <c r="A1012" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1012">
         <v>237</v>
@@ -15206,7 +15209,7 @@
     </row>
     <row r="1016" spans="1:4">
       <c r="A1016" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1017" spans="1:4">
@@ -15253,7 +15256,7 @@
     </row>
     <row r="1020" spans="1:4">
       <c r="A1020" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1020">
         <v>9.1</v>
@@ -15267,7 +15270,7 @@
     </row>
     <row r="1021" spans="1:4">
       <c r="A1021" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1021">
         <v>8.5</v>
@@ -15281,7 +15284,7 @@
     </row>
     <row r="1022" spans="1:4">
       <c r="A1022" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1022">
         <v>31.1</v>
@@ -15295,7 +15298,7 @@
     </row>
     <row r="1023" spans="1:4">
       <c r="A1023" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1023">
         <v>11.3</v>
@@ -15337,7 +15340,7 @@
     </row>
     <row r="1027" spans="1:5">
       <c r="A1027" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1028" spans="1:5">
@@ -15492,7 +15495,7 @@
     </row>
     <row r="1039" spans="1:5">
       <c r="A1039" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1040" spans="1:5">
@@ -15647,7 +15650,7 @@
     </row>
     <row r="1051" spans="1:5">
       <c r="A1051" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1052" spans="1:5">
@@ -15736,7 +15739,7 @@
     </row>
     <row r="1059" spans="1:4">
       <c r="A1059" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1060" spans="1:4">
@@ -15825,7 +15828,7 @@
     </row>
     <row r="1067" spans="1:4">
       <c r="A1067" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1068" spans="1:4">
@@ -15914,7 +15917,7 @@
     </row>
     <row r="1075" spans="1:4">
       <c r="A1075" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1076" spans="1:4">
@@ -16003,7 +16006,7 @@
     </row>
     <row r="1083" spans="1:4">
       <c r="A1083" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1084" spans="1:4">
@@ -16064,7 +16067,7 @@
     </row>
     <row r="1089" spans="1:4">
       <c r="A1089" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1090" spans="1:4">
@@ -16125,7 +16128,7 @@
     </row>
     <row r="1095" spans="1:4">
       <c r="A1095" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1096" spans="1:4">
@@ -16186,7 +16189,7 @@
     </row>
     <row r="1101" spans="1:4">
       <c r="A1101" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1102" spans="1:4">
@@ -16247,7 +16250,7 @@
     </row>
     <row r="1107" spans="1:4">
       <c r="A1107" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1108" spans="1:4">
@@ -16308,7 +16311,7 @@
     </row>
     <row r="1113" spans="1:4">
       <c r="A1113" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1114" spans="1:4">
@@ -16369,7 +16372,7 @@
     </row>
     <row r="1119" spans="1:4">
       <c r="A1119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1120" spans="1:4">
@@ -16416,7 +16419,7 @@
     </row>
     <row r="1123" spans="1:4">
       <c r="A1123" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1123">
         <v>392</v>
@@ -16430,7 +16433,7 @@
     </row>
     <row r="1124" spans="1:4">
       <c r="A1124" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1124">
         <v>492</v>
@@ -16444,7 +16447,7 @@
     </row>
     <row r="1125" spans="1:4">
       <c r="A1125" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1125">
         <v>1213</v>
@@ -16458,7 +16461,7 @@
     </row>
     <row r="1126" spans="1:4">
       <c r="A1126" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1126">
         <v>751</v>
@@ -16500,7 +16503,7 @@
     </row>
     <row r="1130" spans="1:4">
       <c r="A1130" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1131" spans="1:4">
@@ -16547,7 +16550,7 @@
     </row>
     <row r="1134" spans="1:4">
       <c r="A1134" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1134">
         <v>9.4</v>
@@ -16561,7 +16564,7 @@
     </row>
     <row r="1135" spans="1:4">
       <c r="A1135" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1135">
         <v>11.8</v>
@@ -16575,7 +16578,7 @@
     </row>
     <row r="1136" spans="1:4">
       <c r="A1136" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1136">
         <v>29.1</v>
@@ -16589,7 +16592,7 @@
     </row>
     <row r="1137" spans="1:5">
       <c r="A1137" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1137">
         <v>18</v>
@@ -16631,7 +16634,7 @@
     </row>
     <row r="1141" spans="1:5">
       <c r="A1141" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1142" spans="1:5">
@@ -16786,7 +16789,7 @@
     </row>
     <row r="1153" spans="1:5">
       <c r="A1153" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1154" spans="1:5">
@@ -16941,7 +16944,7 @@
     </row>
     <row r="1165" spans="1:5">
       <c r="A1165" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1166" spans="1:5">
@@ -17030,7 +17033,7 @@
     </row>
     <row r="1173" spans="1:4">
       <c r="A1173" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1174" spans="1:4">
@@ -17119,7 +17122,7 @@
     </row>
     <row r="1181" spans="1:4">
       <c r="A1181" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1182" spans="1:4">
@@ -17208,7 +17211,7 @@
     </row>
     <row r="1189" spans="1:4">
       <c r="A1189" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1190" spans="1:4">
@@ -17297,7 +17300,7 @@
     </row>
     <row r="1197" spans="1:4">
       <c r="A1197" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1198" spans="1:4">
@@ -17358,7 +17361,7 @@
     </row>
     <row r="1203" spans="1:4">
       <c r="A1203" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1204" spans="1:4">
@@ -17419,7 +17422,7 @@
     </row>
     <row r="1209" spans="1:4">
       <c r="A1209" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1210" spans="1:4">
@@ -17480,7 +17483,7 @@
     </row>
     <row r="1215" spans="1:4">
       <c r="A1215" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1216" spans="1:4">
@@ -17541,7 +17544,7 @@
     </row>
     <row r="1221" spans="1:4">
       <c r="A1221" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1222" spans="1:4">
@@ -17602,7 +17605,7 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1228" spans="1:4">
@@ -17663,7 +17666,7 @@
     </row>
     <row r="1233" spans="1:4">
       <c r="A1233" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1234" spans="1:4">
@@ -17710,7 +17713,7 @@
     </row>
     <row r="1237" spans="1:4">
       <c r="A1237" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1237">
         <v>492</v>
@@ -17724,7 +17727,7 @@
     </row>
     <row r="1238" spans="1:4">
       <c r="A1238" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1238">
         <v>574</v>
@@ -17738,7 +17741,7 @@
     </row>
     <row r="1239" spans="1:4">
       <c r="A1239" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1239">
         <v>1374</v>
@@ -17752,7 +17755,7 @@
     </row>
     <row r="1240" spans="1:4">
       <c r="A1240" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1240">
         <v>1047</v>
@@ -17794,7 +17797,7 @@
     </row>
     <row r="1244" spans="1:4">
       <c r="A1244" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="1245" spans="1:4">
@@ -17841,7 +17844,7 @@
     </row>
     <row r="1248" spans="1:4">
       <c r="A1248" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1248">
         <v>9.6</v>
@@ -17855,7 +17858,7 @@
     </row>
     <row r="1249" spans="1:5">
       <c r="A1249" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1249">
         <v>11.2</v>
@@ -17869,7 +17872,7 @@
     </row>
     <row r="1250" spans="1:5">
       <c r="A1250" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1250">
         <v>26.8</v>
@@ -17883,7 +17886,7 @@
     </row>
     <row r="1251" spans="1:5">
       <c r="A1251" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1251">
         <v>20.4</v>
@@ -17925,7 +17928,7 @@
     </row>
     <row r="1255" spans="1:5">
       <c r="A1255" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1256" spans="1:5">
@@ -18080,7 +18083,7 @@
     </row>
     <row r="1267" spans="1:5">
       <c r="A1267" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1268" spans="1:5">
@@ -18235,7 +18238,7 @@
     </row>
     <row r="1279" spans="1:5">
       <c r="A1279" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1280" spans="1:5">
@@ -18324,7 +18327,7 @@
     </row>
     <row r="1287" spans="1:4">
       <c r="A1287" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1288" spans="1:4">
@@ -18413,7 +18416,7 @@
     </row>
     <row r="1295" spans="1:4">
       <c r="A1295" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1296" spans="1:4">
@@ -18502,7 +18505,7 @@
     </row>
     <row r="1303" spans="1:4">
       <c r="A1303" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1304" spans="1:4">
@@ -18591,7 +18594,7 @@
     </row>
     <row r="1311" spans="1:4">
       <c r="A1311" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1312" spans="1:4">
@@ -18652,7 +18655,7 @@
     </row>
     <row r="1317" spans="1:4">
       <c r="A1317" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1318" spans="1:4">
@@ -18713,7 +18716,7 @@
     </row>
     <row r="1323" spans="1:4">
       <c r="A1323" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1324" spans="1:4">
@@ -18774,7 +18777,7 @@
     </row>
     <row r="1329" spans="1:4">
       <c r="A1329" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1330" spans="1:4">
@@ -18835,7 +18838,7 @@
     </row>
     <row r="1335" spans="1:4">
       <c r="A1335" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1336" spans="1:4">
@@ -18896,7 +18899,7 @@
     </row>
     <row r="1341" spans="1:4">
       <c r="A1341" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1342" spans="1:4">
@@ -18957,7 +18960,7 @@
     </row>
     <row r="1347" spans="1:4">
       <c r="A1347" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1348" spans="1:4">
@@ -19004,7 +19007,7 @@
     </row>
     <row r="1351" spans="1:4">
       <c r="A1351" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1351">
         <v>124</v>
@@ -19018,7 +19021,7 @@
     </row>
     <row r="1352" spans="1:4">
       <c r="A1352" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1352">
         <v>175</v>
@@ -19032,7 +19035,7 @@
     </row>
     <row r="1353" spans="1:4">
       <c r="A1353" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1353">
         <v>374</v>
@@ -19046,7 +19049,7 @@
     </row>
     <row r="1354" spans="1:4">
       <c r="A1354" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1354">
         <v>208</v>
@@ -19088,7 +19091,7 @@
     </row>
     <row r="1358" spans="1:4">
       <c r="A1358" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1359" spans="1:4">
@@ -19135,7 +19138,7 @@
     </row>
     <row r="1362" spans="1:4">
       <c r="A1362" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1362">
         <v>9.5</v>
@@ -19149,7 +19152,7 @@
     </row>
     <row r="1363" spans="1:4">
       <c r="A1363" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1363">
         <v>13.4</v>
@@ -19163,7 +19166,7 @@
     </row>
     <row r="1364" spans="1:4">
       <c r="A1364" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1364">
         <v>28.5</v>
@@ -19177,7 +19180,7 @@
     </row>
     <row r="1365" spans="1:4">
       <c r="A1365" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1365">
         <v>15.9</v>
@@ -19219,7 +19222,7 @@
     </row>
     <row r="1369" spans="1:4">
       <c r="A1369" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1370" spans="1:4">
@@ -19344,7 +19347,7 @@
     </row>
     <row r="1381" spans="1:4">
       <c r="A1381" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1382" spans="1:4">
@@ -19469,7 +19472,7 @@
     </row>
     <row r="1393" spans="1:3">
       <c r="A1393" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1394" spans="1:3">
@@ -19540,7 +19543,7 @@
     </row>
     <row r="1401" spans="1:3">
       <c r="A1401" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1402" spans="1:3">
@@ -19611,7 +19614,7 @@
     </row>
     <row r="1409" spans="1:3">
       <c r="A1409" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1410" spans="1:3">
@@ -19682,7 +19685,7 @@
     </row>
     <row r="1417" spans="1:3">
       <c r="A1417" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1418" spans="1:3">
@@ -19753,7 +19756,7 @@
     </row>
     <row r="1425" spans="1:3">
       <c r="A1425" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1426" spans="1:3">
@@ -19802,7 +19805,7 @@
     </row>
     <row r="1431" spans="1:3">
       <c r="A1431" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="1432" spans="1:3">
@@ -19851,7 +19854,7 @@
     </row>
     <row r="1437" spans="1:3">
       <c r="A1437" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1438" spans="1:3">
@@ -19900,7 +19903,7 @@
     </row>
     <row r="1443" spans="1:3">
       <c r="A1443" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1444" spans="1:3">
@@ -19949,7 +19952,7 @@
     </row>
     <row r="1449" spans="1:3">
       <c r="A1449" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1450" spans="1:3">
@@ -19998,7 +20001,7 @@
     </row>
     <row r="1455" spans="1:3">
       <c r="A1455" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1456" spans="1:3">
@@ -20047,7 +20050,7 @@
     </row>
     <row r="1461" spans="1:3">
       <c r="A1461" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1462" spans="1:3">
@@ -20085,7 +20088,7 @@
     </row>
     <row r="1465" spans="1:3">
       <c r="A1465" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1465">
         <v>358</v>
@@ -20096,7 +20099,7 @@
     </row>
     <row r="1466" spans="1:3">
       <c r="A1466" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1466">
         <v>391</v>
@@ -20107,7 +20110,7 @@
     </row>
     <row r="1467" spans="1:3">
       <c r="A1467" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1467">
         <v>970</v>
@@ -20118,7 +20121,7 @@
     </row>
     <row r="1468" spans="1:3">
       <c r="A1468" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1468">
         <v>827</v>
@@ -20151,7 +20154,7 @@
     </row>
     <row r="1472" spans="1:3">
       <c r="A1472" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1473" spans="1:5">
@@ -20189,7 +20192,7 @@
     </row>
     <row r="1476" spans="1:5">
       <c r="A1476" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1476">
         <v>9.699999999999999</v>
@@ -20200,7 +20203,7 @@
     </row>
     <row r="1477" spans="1:5">
       <c r="A1477" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1477">
         <v>10.5</v>
@@ -20211,7 +20214,7 @@
     </row>
     <row r="1478" spans="1:5">
       <c r="A1478" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1478">
         <v>26.2</v>
@@ -20222,7 +20225,7 @@
     </row>
     <row r="1479" spans="1:5">
       <c r="A1479" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1479">
         <v>22.3</v>
@@ -20255,7 +20258,7 @@
     </row>
     <row r="1483" spans="1:5">
       <c r="A1483" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1484" spans="1:5">
@@ -20410,7 +20413,7 @@
     </row>
     <row r="1495" spans="1:5">
       <c r="A1495" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1496" spans="1:5">
@@ -20565,7 +20568,7 @@
     </row>
     <row r="1507" spans="1:5">
       <c r="A1507" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1508" spans="1:5">
@@ -20654,7 +20657,7 @@
     </row>
     <row r="1515" spans="1:5">
       <c r="A1515" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1516" spans="1:5">
@@ -20743,7 +20746,7 @@
     </row>
     <row r="1523" spans="1:4">
       <c r="A1523" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1524" spans="1:4">
@@ -20832,7 +20835,7 @@
     </row>
     <row r="1531" spans="1:4">
       <c r="A1531" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1532" spans="1:4">
@@ -20921,7 +20924,7 @@
     </row>
     <row r="1539" spans="1:4">
       <c r="A1539" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1540" spans="1:4">
@@ -20982,7 +20985,7 @@
     </row>
     <row r="1545" spans="1:4">
       <c r="A1545" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1546" spans="1:4">
@@ -21043,7 +21046,7 @@
     </row>
     <row r="1551" spans="1:4">
       <c r="A1551" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1552" spans="1:4">
@@ -21104,7 +21107,7 @@
     </row>
     <row r="1557" spans="1:4">
       <c r="A1557" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1558" spans="1:4">
@@ -21165,7 +21168,7 @@
     </row>
     <row r="1563" spans="1:4">
       <c r="A1563" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1564" spans="1:4">
@@ -21226,7 +21229,7 @@
     </row>
     <row r="1569" spans="1:4">
       <c r="A1569" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1570" spans="1:4">
@@ -21287,7 +21290,7 @@
     </row>
     <row r="1575" spans="1:4">
       <c r="A1575" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1576" spans="1:4">
@@ -21334,7 +21337,7 @@
     </row>
     <row r="1579" spans="1:4">
       <c r="A1579" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1579">
         <v>412</v>
@@ -21348,7 +21351,7 @@
     </row>
     <row r="1580" spans="1:4">
       <c r="A1580" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1580">
         <v>467</v>
@@ -21362,7 +21365,7 @@
     </row>
     <row r="1581" spans="1:4">
       <c r="A1581" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1581">
         <v>1161</v>
@@ -21376,7 +21379,7 @@
     </row>
     <row r="1582" spans="1:4">
       <c r="A1582" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1582">
         <v>903</v>
@@ -21418,7 +21421,7 @@
     </row>
     <row r="1586" spans="1:5">
       <c r="A1586" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1587" spans="1:5">
@@ -21465,7 +21468,7 @@
     </row>
     <row r="1590" spans="1:5">
       <c r="A1590" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1590">
         <v>9.5</v>
@@ -21479,7 +21482,7 @@
     </row>
     <row r="1591" spans="1:5">
       <c r="A1591" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1591">
         <v>10.8</v>
@@ -21493,7 +21496,7 @@
     </row>
     <row r="1592" spans="1:5">
       <c r="A1592" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1592">
         <v>26.8</v>
@@ -21507,7 +21510,7 @@
     </row>
     <row r="1593" spans="1:5">
       <c r="A1593" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1593">
         <v>20.9</v>
@@ -21549,7 +21552,7 @@
     </row>
     <row r="1597" spans="1:5">
       <c r="A1597" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1598" spans="1:5">
@@ -21704,7 +21707,7 @@
     </row>
     <row r="1609" spans="1:5">
       <c r="A1609" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1610" spans="1:5">
@@ -21859,7 +21862,7 @@
     </row>
     <row r="1621" spans="1:5">
       <c r="A1621" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1622" spans="1:5">
@@ -21948,7 +21951,7 @@
     </row>
     <row r="1629" spans="1:5">
       <c r="A1629" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1630" spans="1:5">
@@ -22037,7 +22040,7 @@
     </row>
     <row r="1637" spans="1:4">
       <c r="A1637" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1638" spans="1:4">
@@ -22126,7 +22129,7 @@
     </row>
     <row r="1645" spans="1:4">
       <c r="A1645" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1646" spans="1:4">
@@ -22215,7 +22218,7 @@
     </row>
     <row r="1653" spans="1:4">
       <c r="A1653" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1654" spans="1:4">
@@ -22276,7 +22279,7 @@
     </row>
     <row r="1659" spans="1:4">
       <c r="A1659" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1660" spans="1:4">
@@ -22337,7 +22340,7 @@
     </row>
     <row r="1665" spans="1:4">
       <c r="A1665" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="1666" spans="1:4">
@@ -22398,7 +22401,7 @@
     </row>
     <row r="1671" spans="1:4">
       <c r="A1671" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="1672" spans="1:4">
@@ -22459,7 +22462,7 @@
     </row>
     <row r="1677" spans="1:4">
       <c r="A1677" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1678" spans="1:4">
@@ -22520,7 +22523,7 @@
     </row>
     <row r="1683" spans="1:4">
       <c r="A1683" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1684" spans="1:4">
@@ -22581,7 +22584,7 @@
     </row>
     <row r="1689" spans="1:4">
       <c r="A1689" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="1690" spans="1:4">
@@ -22628,7 +22631,7 @@
     </row>
     <row r="1693" spans="1:4">
       <c r="A1693" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1693">
         <v>80</v>
@@ -22642,7 +22645,7 @@
     </row>
     <row r="1694" spans="1:4">
       <c r="A1694" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1694">
         <v>104</v>
@@ -22656,7 +22659,7 @@
     </row>
     <row r="1695" spans="1:4">
       <c r="A1695" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1695">
         <v>246</v>
@@ -22670,7 +22673,7 @@
     </row>
     <row r="1696" spans="1:4">
       <c r="A1696" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1696">
         <v>142</v>
@@ -22712,7 +22715,7 @@
     </row>
     <row r="1700" spans="1:5">
       <c r="A1700" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="1701" spans="1:5">
@@ -22759,7 +22762,7 @@
     </row>
     <row r="1704" spans="1:5">
       <c r="A1704" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1704">
         <v>9.300000000000001</v>
@@ -22773,7 +22776,7 @@
     </row>
     <row r="1705" spans="1:5">
       <c r="A1705" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1705">
         <v>12.1</v>
@@ -22787,7 +22790,7 @@
     </row>
     <row r="1706" spans="1:5">
       <c r="A1706" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1706">
         <v>28.5</v>
@@ -22801,7 +22804,7 @@
     </row>
     <row r="1707" spans="1:5">
       <c r="A1707" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1707">
         <v>16.5</v>
@@ -22843,7 +22846,7 @@
     </row>
     <row r="1711" spans="1:5">
       <c r="A1711" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1712" spans="1:5">
@@ -22998,7 +23001,7 @@
     </row>
     <row r="1723" spans="1:5">
       <c r="A1723" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1724" spans="1:5">
@@ -23153,7 +23156,7 @@
     </row>
     <row r="1735" spans="1:5">
       <c r="A1735" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1736" spans="1:5">
@@ -23242,7 +23245,7 @@
     </row>
     <row r="1743" spans="1:5">
       <c r="A1743" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1744" spans="1:5">
@@ -23331,7 +23334,7 @@
     </row>
     <row r="1751" spans="1:4">
       <c r="A1751" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1752" spans="1:4">
@@ -23420,7 +23423,7 @@
     </row>
     <row r="1759" spans="1:4">
       <c r="A1759" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="1760" spans="1:4">
@@ -23509,7 +23512,7 @@
     </row>
     <row r="1767" spans="1:4">
       <c r="A1767" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1768" spans="1:4">
@@ -23570,7 +23573,7 @@
     </row>
     <row r="1773" spans="1:4">
       <c r="A1773" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1774" spans="1:4">
@@ -23631,7 +23634,7 @@
     </row>
     <row r="1779" spans="1:4">
       <c r="A1779" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1780" spans="1:4">
@@ -23692,7 +23695,7 @@
     </row>
     <row r="1785" spans="1:4">
       <c r="A1785" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1786" spans="1:4">
@@ -23753,7 +23756,7 @@
     </row>
     <row r="1791" spans="1:4">
       <c r="A1791" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1792" spans="1:4">
@@ -23814,7 +23817,7 @@
     </row>
     <row r="1797" spans="1:4">
       <c r="A1797" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1798" spans="1:4">
@@ -23875,7 +23878,7 @@
     </row>
     <row r="1803" spans="1:4">
       <c r="A1803" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1804" spans="1:4">
@@ -23922,7 +23925,7 @@
     </row>
     <row r="1807" spans="1:4">
       <c r="A1807" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1807">
         <v>324</v>
@@ -23936,7 +23939,7 @@
     </row>
     <row r="1808" spans="1:4">
       <c r="A1808" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1808">
         <v>359</v>
@@ -23950,7 +23953,7 @@
     </row>
     <row r="1809" spans="1:4">
       <c r="A1809" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1809">
         <v>894</v>
@@ -23964,7 +23967,7 @@
     </row>
     <row r="1810" spans="1:4">
       <c r="A1810" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1810">
         <v>750</v>
@@ -24006,7 +24009,7 @@
     </row>
     <row r="1814" spans="1:4">
       <c r="A1814" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1815" spans="1:4">
@@ -24053,7 +24056,7 @@
     </row>
     <row r="1818" spans="1:4">
       <c r="A1818" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1818">
         <v>9.6</v>
@@ -24067,7 +24070,7 @@
     </row>
     <row r="1819" spans="1:4">
       <c r="A1819" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1819">
         <v>10.6</v>
@@ -24081,7 +24084,7 @@
     </row>
     <row r="1820" spans="1:4">
       <c r="A1820" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1820">
         <v>26.4</v>
@@ -24095,7 +24098,7 @@
     </row>
     <row r="1821" spans="1:4">
       <c r="A1821" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1821">
         <v>22.1</v>
@@ -24137,7 +24140,7 @@
     </row>
     <row r="1825" spans="1:5">
       <c r="A1825" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1826" spans="1:5">
@@ -24292,7 +24295,7 @@
     </row>
     <row r="1837" spans="1:5">
       <c r="A1837" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1838" spans="1:5">
@@ -24447,7 +24450,7 @@
     </row>
     <row r="1849" spans="1:5">
       <c r="A1849" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1850" spans="1:5">
@@ -24536,7 +24539,7 @@
     </row>
     <row r="1857" spans="1:4">
       <c r="A1857" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1858" spans="1:4">
@@ -24625,7 +24628,7 @@
     </row>
     <row r="1865" spans="1:4">
       <c r="A1865" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1866" spans="1:4">
@@ -24714,7 +24717,7 @@
     </row>
     <row r="1873" spans="1:4">
       <c r="A1873" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1874" spans="1:4">
@@ -24803,7 +24806,7 @@
     </row>
     <row r="1881" spans="1:4">
       <c r="A1881" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="1882" spans="1:4">
@@ -24864,7 +24867,7 @@
     </row>
     <row r="1887" spans="1:4">
       <c r="A1887" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1888" spans="1:4">
@@ -24925,7 +24928,7 @@
     </row>
     <row r="1893" spans="1:4">
       <c r="A1893" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="1894" spans="1:4">
@@ -24986,7 +24989,7 @@
     </row>
     <row r="1899" spans="1:4">
       <c r="A1899" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="1900" spans="1:4">
@@ -25047,7 +25050,7 @@
     </row>
     <row r="1905" spans="1:4">
       <c r="A1905" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1906" spans="1:4">
@@ -25108,7 +25111,7 @@
     </row>
     <row r="1911" spans="1:4">
       <c r="A1911" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="1912" spans="1:4">
@@ -25169,7 +25172,7 @@
     </row>
     <row r="1917" spans="1:4">
       <c r="A1917" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1918" spans="1:4">
@@ -25216,7 +25219,7 @@
     </row>
     <row r="1921" spans="1:4">
       <c r="A1921" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1921">
         <v>450</v>
@@ -25230,7 +25233,7 @@
     </row>
     <row r="1922" spans="1:4">
       <c r="A1922" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1922">
         <v>514</v>
@@ -25244,7 +25247,7 @@
     </row>
     <row r="1923" spans="1:4">
       <c r="A1923" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1923">
         <v>1260</v>
@@ -25258,7 +25261,7 @@
     </row>
     <row r="1924" spans="1:4">
       <c r="A1924" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1924">
         <v>964</v>
@@ -25300,7 +25303,7 @@
     </row>
     <row r="1928" spans="1:4">
       <c r="A1928" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1929" spans="1:4">
@@ -25347,7 +25350,7 @@
     </row>
     <row r="1932" spans="1:4">
       <c r="A1932" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B1932">
         <v>9.5</v>
@@ -25361,7 +25364,7 @@
     </row>
     <row r="1933" spans="1:4">
       <c r="A1933" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1933">
         <v>10.9</v>
@@ -25375,7 +25378,7 @@
     </row>
     <row r="1934" spans="1:4">
       <c r="A1934" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1934">
         <v>26.6</v>
@@ -25389,7 +25392,7 @@
     </row>
     <row r="1935" spans="1:4">
       <c r="A1935" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1935">
         <v>20.4</v>
@@ -25431,7 +25434,7 @@
     </row>
     <row r="1939" spans="1:5">
       <c r="A1939" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1940" spans="1:5">
@@ -25586,7 +25589,7 @@
     </row>
     <row r="1951" spans="1:5">
       <c r="A1951" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1952" spans="1:5">
@@ -25741,7 +25744,7 @@
     </row>
     <row r="1963" spans="1:5">
       <c r="A1963" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1964" spans="1:5">
@@ -25830,7 +25833,7 @@
     </row>
     <row r="1971" spans="1:4">
       <c r="A1971" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1972" spans="1:4">
@@ -25919,7 +25922,7 @@
     </row>
     <row r="1979" spans="1:4">
       <c r="A1979" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1980" spans="1:4">
@@ -26008,7 +26011,7 @@
     </row>
     <row r="1987" spans="1:4">
       <c r="A1987" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1988" spans="1:4">
@@ -26097,7 +26100,7 @@
     </row>
     <row r="1995" spans="1:4">
       <c r="A1995" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1996" spans="1:4">
@@ -26158,7 +26161,7 @@
     </row>
     <row r="2001" spans="1:4">
       <c r="A2001" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2002" spans="1:4">
@@ -26219,7 +26222,7 @@
     </row>
     <row r="2007" spans="1:4">
       <c r="A2007" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2008" spans="1:4">
@@ -26280,7 +26283,7 @@
     </row>
     <row r="2013" spans="1:4">
       <c r="A2013" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2014" spans="1:4">
@@ -26341,7 +26344,7 @@
     </row>
     <row r="2019" spans="1:4">
       <c r="A2019" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2020" spans="1:4">
@@ -26402,7 +26405,7 @@
     </row>
     <row r="2025" spans="1:4">
       <c r="A2025" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2026" spans="1:4">
@@ -26463,7 +26466,7 @@
     </row>
     <row r="2031" spans="1:4">
       <c r="A2031" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2032" spans="1:4">
@@ -26510,7 +26513,7 @@
     </row>
     <row r="2035" spans="1:4">
       <c r="A2035" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2035">
         <v>106</v>
@@ -26524,7 +26527,7 @@
     </row>
     <row r="2036" spans="1:4">
       <c r="A2036" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2036">
         <v>158</v>
@@ -26538,7 +26541,7 @@
     </row>
     <row r="2037" spans="1:4">
       <c r="A2037" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2037">
         <v>339</v>
@@ -26552,7 +26555,7 @@
     </row>
     <row r="2038" spans="1:4">
       <c r="A2038" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2038">
         <v>209</v>
@@ -26594,7 +26597,7 @@
     </row>
     <row r="2042" spans="1:4">
       <c r="A2042" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2043" spans="1:4">
@@ -26641,7 +26644,7 @@
     </row>
     <row r="2046" spans="1:4">
       <c r="A2046" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2046">
         <v>8.699999999999999</v>
@@ -26655,7 +26658,7 @@
     </row>
     <row r="2047" spans="1:4">
       <c r="A2047" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2047">
         <v>13</v>
@@ -26669,7 +26672,7 @@
     </row>
     <row r="2048" spans="1:4">
       <c r="A2048" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2048">
         <v>28</v>
@@ -26683,7 +26686,7 @@
     </row>
     <row r="2049" spans="1:5">
       <c r="A2049" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2049">
         <v>17.2</v>
@@ -26725,7 +26728,7 @@
     </row>
     <row r="2053" spans="1:5">
       <c r="A2053" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2054" spans="1:5">
@@ -26880,7 +26883,7 @@
     </row>
     <row r="2065" spans="1:5">
       <c r="A2065" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2066" spans="1:5">
@@ -27035,7 +27038,7 @@
     </row>
     <row r="2077" spans="1:5">
       <c r="A2077" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2078" spans="1:5">
@@ -27124,7 +27127,7 @@
     </row>
     <row r="2085" spans="1:4">
       <c r="A2085" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2086" spans="1:4">
@@ -27213,7 +27216,7 @@
     </row>
     <row r="2093" spans="1:4">
       <c r="A2093" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2094" spans="1:4">
@@ -27302,7 +27305,7 @@
     </row>
     <row r="2101" spans="1:4">
       <c r="A2101" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2102" spans="1:4">
@@ -27391,7 +27394,7 @@
     </row>
     <row r="2109" spans="1:4">
       <c r="A2109" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2110" spans="1:4">
@@ -27452,7 +27455,7 @@
     </row>
     <row r="2115" spans="1:4">
       <c r="A2115" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2116" spans="1:4">
@@ -27513,7 +27516,7 @@
     </row>
     <row r="2121" spans="1:4">
       <c r="A2121" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2122" spans="1:4">
@@ -27574,7 +27577,7 @@
     </row>
     <row r="2127" spans="1:4">
       <c r="A2127" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2128" spans="1:4">
@@ -27635,7 +27638,7 @@
     </row>
     <row r="2133" spans="1:4">
       <c r="A2133" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2134" spans="1:4">
@@ -27696,7 +27699,7 @@
     </row>
     <row r="2139" spans="1:4">
       <c r="A2139" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2140" spans="1:4">
@@ -27757,7 +27760,7 @@
     </row>
     <row r="2145" spans="1:4">
       <c r="A2145" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2146" spans="1:4">
@@ -27804,7 +27807,7 @@
     </row>
     <row r="2149" spans="1:4">
       <c r="A2149" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2149">
         <v>335</v>
@@ -27818,7 +27821,7 @@
     </row>
     <row r="2150" spans="1:4">
       <c r="A2150" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2150">
         <v>348</v>
@@ -27832,7 +27835,7 @@
     </row>
     <row r="2151" spans="1:4">
       <c r="A2151" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2151">
         <v>891</v>
@@ -27846,7 +27849,7 @@
     </row>
     <row r="2152" spans="1:4">
       <c r="A2152" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2152">
         <v>744</v>
@@ -27888,7 +27891,7 @@
     </row>
     <row r="2156" spans="1:4">
       <c r="A2156" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2157" spans="1:4">
@@ -27935,7 +27938,7 @@
     </row>
     <row r="2160" spans="1:4">
       <c r="A2160" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2160">
         <v>9.800000000000001</v>
@@ -27949,7 +27952,7 @@
     </row>
     <row r="2161" spans="1:6">
       <c r="A2161" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2161">
         <v>10.2</v>
@@ -27963,7 +27966,7 @@
     </row>
     <row r="2162" spans="1:6">
       <c r="A2162" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2162">
         <v>26</v>
@@ -27977,7 +27980,7 @@
     </row>
     <row r="2163" spans="1:6">
       <c r="A2163" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2163">
         <v>21.7</v>
@@ -28019,7 +28022,7 @@
     </row>
     <row r="2167" spans="1:6">
       <c r="A2167" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2168" spans="1:6">
@@ -28030,13 +28033,13 @@
         <v>7</v>
       </c>
       <c r="C2168" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D2168" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2168" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F2168" s="1" t="s">
         <v>5</v>
@@ -28204,7 +28207,7 @@
     </row>
     <row r="2179" spans="1:6">
       <c r="A2179" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2180" spans="1:6">
@@ -28215,13 +28218,13 @@
         <v>7</v>
       </c>
       <c r="C2180" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D2180" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2180" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F2180" s="1" t="s">
         <v>5</v>
@@ -28389,7 +28392,7 @@
     </row>
     <row r="2191" spans="1:6">
       <c r="A2191" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2192" spans="1:6">
@@ -28397,13 +28400,13 @@
         <v>16</v>
       </c>
       <c r="B2192" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2192" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2192" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2192" s="1" t="s">
         <v>5</v>
@@ -28496,7 +28499,7 @@
     </row>
     <row r="2199" spans="1:5">
       <c r="A2199" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2200" spans="1:5">
@@ -28504,13 +28507,13 @@
         <v>16</v>
       </c>
       <c r="B2200" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2200" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2200" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2200" s="1" t="s">
         <v>5</v>
@@ -28603,7 +28606,7 @@
     </row>
     <row r="2207" spans="1:5">
       <c r="A2207" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2208" spans="1:5">
@@ -28611,13 +28614,13 @@
         <v>23</v>
       </c>
       <c r="B2208" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2208" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2208" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2208" s="1" t="s">
         <v>5</v>
@@ -28710,7 +28713,7 @@
     </row>
     <row r="2215" spans="1:5">
       <c r="A2215" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2216" spans="1:5">
@@ -28718,13 +28721,13 @@
         <v>23</v>
       </c>
       <c r="B2216" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2216" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2216" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2216" s="1" t="s">
         <v>5</v>
@@ -28817,7 +28820,7 @@
     </row>
     <row r="2223" spans="1:5">
       <c r="A2223" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2224" spans="1:5">
@@ -28825,13 +28828,13 @@
         <v>26</v>
       </c>
       <c r="B2224" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2224" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2224" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2224" s="1" t="s">
         <v>5</v>
@@ -28890,7 +28893,7 @@
     </row>
     <row r="2229" spans="1:5">
       <c r="A2229" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2230" spans="1:5">
@@ -28898,13 +28901,13 @@
         <v>26</v>
       </c>
       <c r="B2230" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2230" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2230" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2230" s="1" t="s">
         <v>5</v>
@@ -28963,7 +28966,7 @@
     </row>
     <row r="2235" spans="1:5">
       <c r="A2235" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2236" spans="1:5">
@@ -28971,13 +28974,13 @@
         <v>29</v>
       </c>
       <c r="B2236" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2236" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2236" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2236" s="1" t="s">
         <v>5</v>
@@ -29036,7 +29039,7 @@
     </row>
     <row r="2241" spans="1:5">
       <c r="A2241" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2242" spans="1:5">
@@ -29044,13 +29047,13 @@
         <v>29</v>
       </c>
       <c r="B2242" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2242" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2242" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2242" s="1" t="s">
         <v>5</v>
@@ -29109,7 +29112,7 @@
     </row>
     <row r="2247" spans="1:5">
       <c r="A2247" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2248" spans="1:5">
@@ -29117,13 +29120,13 @@
         <v>32</v>
       </c>
       <c r="B2248" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2248" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2248" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2248" s="1" t="s">
         <v>5</v>
@@ -29179,7 +29182,7 @@
     </row>
     <row r="2253" spans="1:5">
       <c r="A2253" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2254" spans="1:5">
@@ -29187,13 +29190,13 @@
         <v>32</v>
       </c>
       <c r="B2254" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2254" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2254" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2254" s="1" t="s">
         <v>5</v>
@@ -29249,7 +29252,7 @@
     </row>
     <row r="2259" spans="1:5">
       <c r="A2259" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2260" spans="1:5">
@@ -29257,13 +29260,13 @@
         <v>37</v>
       </c>
       <c r="B2260" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2260" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2260" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2260" s="1" t="s">
         <v>5</v>
@@ -29305,7 +29308,7 @@
     </row>
     <row r="2263" spans="1:5">
       <c r="A2263" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2263">
         <v>14</v>
@@ -29322,7 +29325,7 @@
     </row>
     <row r="2264" spans="1:5">
       <c r="A2264" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2264">
         <v>24</v>
@@ -29339,7 +29342,7 @@
     </row>
     <row r="2265" spans="1:5">
       <c r="A2265" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2265">
         <v>48</v>
@@ -29356,7 +29359,7 @@
     </row>
     <row r="2266" spans="1:5">
       <c r="A2266" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2266">
         <v>23</v>
@@ -29407,7 +29410,7 @@
     </row>
     <row r="2270" spans="1:5">
       <c r="A2270" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2271" spans="1:5">
@@ -29415,13 +29418,13 @@
         <v>37</v>
       </c>
       <c r="B2271" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C2271" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2271" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2271" s="1" t="s">
         <v>5</v>
@@ -29463,7 +29466,7 @@
     </row>
     <row r="2274" spans="1:5">
       <c r="A2274" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2274">
         <v>8.199999999999999</v>
@@ -29480,7 +29483,7 @@
     </row>
     <row r="2275" spans="1:5">
       <c r="A2275" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2275">
         <v>14</v>
@@ -29497,7 +29500,7 @@
     </row>
     <row r="2276" spans="1:5">
       <c r="A2276" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2276">
         <v>28.1</v>
@@ -29514,7 +29517,7 @@
     </row>
     <row r="2277" spans="1:5">
       <c r="A2277" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2277">
         <v>13.5</v>
@@ -29565,7 +29568,7 @@
     </row>
     <row r="2281" spans="1:5">
       <c r="A2281" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2282" spans="1:5">
@@ -29720,7 +29723,7 @@
     </row>
     <row r="2293" spans="1:5">
       <c r="A2293" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2294" spans="1:5">
@@ -29875,7 +29878,7 @@
     </row>
     <row r="2305" spans="1:4">
       <c r="A2305" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2306" spans="1:4">
@@ -29964,7 +29967,7 @@
     </row>
     <row r="2313" spans="1:4">
       <c r="A2313" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2314" spans="1:4">
@@ -30053,7 +30056,7 @@
     </row>
     <row r="2321" spans="1:4">
       <c r="A2321" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2322" spans="1:4">
@@ -30142,7 +30145,7 @@
     </row>
     <row r="2329" spans="1:4">
       <c r="A2329" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2330" spans="1:4">
@@ -30231,7 +30234,7 @@
     </row>
     <row r="2337" spans="1:4">
       <c r="A2337" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2338" spans="1:4">
@@ -30292,7 +30295,7 @@
     </row>
     <row r="2343" spans="1:4">
       <c r="A2343" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2344" spans="1:4">
@@ -30353,7 +30356,7 @@
     </row>
     <row r="2349" spans="1:4">
       <c r="A2349" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2350" spans="1:4">
@@ -30414,7 +30417,7 @@
     </row>
     <row r="2355" spans="1:4">
       <c r="A2355" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2356" spans="1:4">
@@ -30475,7 +30478,7 @@
     </row>
     <row r="2361" spans="1:4">
       <c r="A2361" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2362" spans="1:4">
@@ -30536,7 +30539,7 @@
     </row>
     <row r="2367" spans="1:4">
       <c r="A2367" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2368" spans="1:4">
@@ -30597,7 +30600,7 @@
     </row>
     <row r="2373" spans="1:4">
       <c r="A2373" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2374" spans="1:4">
@@ -30644,7 +30647,7 @@
     </row>
     <row r="2377" spans="1:4">
       <c r="A2377" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2377">
         <v>594</v>
@@ -30658,7 +30661,7 @@
     </row>
     <row r="2378" spans="1:4">
       <c r="A2378" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2378">
         <v>606</v>
@@ -30672,7 +30675,7 @@
     </row>
     <row r="2379" spans="1:4">
       <c r="A2379" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2379">
         <v>1411</v>
@@ -30686,7 +30689,7 @@
     </row>
     <row r="2380" spans="1:4">
       <c r="A2380" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2380">
         <v>1114</v>
@@ -30728,7 +30731,7 @@
     </row>
     <row r="2384" spans="1:4">
       <c r="A2384" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2385" spans="1:10">
@@ -30775,7 +30778,7 @@
     </row>
     <row r="2388" spans="1:10">
       <c r="A2388" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2388">
         <v>10.6</v>
@@ -30789,7 +30792,7 @@
     </row>
     <row r="2389" spans="1:10">
       <c r="A2389" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2389">
         <v>10.9</v>
@@ -30803,7 +30806,7 @@
     </row>
     <row r="2390" spans="1:10">
       <c r="A2390" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2390">
         <v>25.3</v>
@@ -30817,7 +30820,7 @@
     </row>
     <row r="2391" spans="1:10">
       <c r="A2391" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2391">
         <v>20</v>
@@ -30859,7 +30862,7 @@
     </row>
     <row r="2395" spans="1:10">
       <c r="A2395" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2396" spans="1:10">
@@ -30870,25 +30873,25 @@
         <v>7</v>
       </c>
       <c r="C2396" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D2396" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E2396" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F2396" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G2396" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H2396" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I2396" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J2396" s="1" t="s">
         <v>5</v>
@@ -31164,7 +31167,7 @@
     </row>
     <row r="2407" spans="1:10">
       <c r="A2407" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2408" spans="1:10">
@@ -31175,25 +31178,25 @@
         <v>7</v>
       </c>
       <c r="C2408" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D2408" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E2408" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F2408" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G2408" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H2408" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I2408" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J2408" s="1" t="s">
         <v>5</v>
@@ -31469,7 +31472,7 @@
     </row>
     <row r="2419" spans="1:10">
       <c r="A2419" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2420" spans="1:10">
@@ -31477,25 +31480,25 @@
         <v>16</v>
       </c>
       <c r="B2420" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2420" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2420" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2420" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2420" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2420" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2420" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2420" s="1" t="s">
         <v>5</v>
@@ -31648,7 +31651,7 @@
     </row>
     <row r="2427" spans="1:10">
       <c r="A2427" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2428" spans="1:10">
@@ -31656,25 +31659,25 @@
         <v>16</v>
       </c>
       <c r="B2428" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2428" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2428" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2428" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2428" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2428" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2428" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2428" s="1" t="s">
         <v>5</v>
@@ -31827,7 +31830,7 @@
     </row>
     <row r="2435" spans="1:9">
       <c r="A2435" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2436" spans="1:9">
@@ -31835,25 +31838,25 @@
         <v>23</v>
       </c>
       <c r="B2436" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2436" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2436" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2436" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2436" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2436" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2436" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2436" s="1" t="s">
         <v>5</v>
@@ -32006,7 +32009,7 @@
     </row>
     <row r="2443" spans="1:9">
       <c r="A2443" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2444" spans="1:9">
@@ -32014,25 +32017,25 @@
         <v>23</v>
       </c>
       <c r="B2444" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2444" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2444" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2444" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2444" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2444" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2444" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2444" s="1" t="s">
         <v>5</v>
@@ -32185,7 +32188,7 @@
     </row>
     <row r="2451" spans="1:9">
       <c r="A2451" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2452" spans="1:9">
@@ -32193,25 +32196,25 @@
         <v>26</v>
       </c>
       <c r="B2452" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2452" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2452" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2452" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2452" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2452" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2452" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2452" s="1" t="s">
         <v>5</v>
@@ -32306,7 +32309,7 @@
     </row>
     <row r="2457" spans="1:9">
       <c r="A2457" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2458" spans="1:9">
@@ -32314,25 +32317,25 @@
         <v>26</v>
       </c>
       <c r="B2458" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2458" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2458" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2458" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2458" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2458" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2458" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2458" s="1" t="s">
         <v>5</v>
@@ -32427,7 +32430,7 @@
     </row>
     <row r="2463" spans="1:9">
       <c r="A2463" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2464" spans="1:9">
@@ -32435,25 +32438,25 @@
         <v>29</v>
       </c>
       <c r="B2464" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2464" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2464" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2464" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2464" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2464" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2464" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2464" s="1" t="s">
         <v>5</v>
@@ -32548,7 +32551,7 @@
     </row>
     <row r="2469" spans="1:9">
       <c r="A2469" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2470" spans="1:9">
@@ -32556,25 +32559,25 @@
         <v>29</v>
       </c>
       <c r="B2470" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2470" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2470" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2470" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2470" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2470" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2470" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2470" s="1" t="s">
         <v>5</v>
@@ -32669,7 +32672,7 @@
     </row>
     <row r="2475" spans="1:9">
       <c r="A2475" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2476" spans="1:9">
@@ -32677,25 +32680,25 @@
         <v>32</v>
       </c>
       <c r="B2476" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2476" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2476" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2476" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2476" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2476" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2476" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2476" s="1" t="s">
         <v>5</v>
@@ -32790,7 +32793,7 @@
     </row>
     <row r="2481" spans="1:9">
       <c r="A2481" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2482" spans="1:9">
@@ -32798,25 +32801,25 @@
         <v>32</v>
       </c>
       <c r="B2482" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2482" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2482" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2482" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2482" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2482" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2482" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2482" s="1" t="s">
         <v>5</v>
@@ -32911,7 +32914,7 @@
     </row>
     <row r="2487" spans="1:9">
       <c r="A2487" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2488" spans="1:9">
@@ -32919,25 +32922,25 @@
         <v>37</v>
       </c>
       <c r="B2488" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2488" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2488" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2488" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2488" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2488" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2488" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2488" s="1" t="s">
         <v>5</v>
@@ -33003,7 +33006,7 @@
     </row>
     <row r="2491" spans="1:9">
       <c r="A2491" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2491">
         <v>222</v>
@@ -33032,7 +33035,7 @@
     </row>
     <row r="2492" spans="1:9">
       <c r="A2492" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2492">
         <v>80</v>
@@ -33061,7 +33064,7 @@
     </row>
     <row r="2493" spans="1:9">
       <c r="A2493" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2493">
         <v>573</v>
@@ -33090,7 +33093,7 @@
     </row>
     <row r="2494" spans="1:9">
       <c r="A2494" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2494">
         <v>301</v>
@@ -33177,7 +33180,7 @@
     </row>
     <row r="2498" spans="1:9">
       <c r="A2498" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2499" spans="1:9">
@@ -33185,25 +33188,25 @@
         <v>37</v>
       </c>
       <c r="B2499" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2499" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2499" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2499" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2499" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G2499" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H2499" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I2499" s="1" t="s">
         <v>5</v>
@@ -33269,7 +33272,7 @@
     </row>
     <row r="2502" spans="1:9">
       <c r="A2502" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B2502">
         <v>12.8</v>
@@ -33298,7 +33301,7 @@
     </row>
     <row r="2503" spans="1:9">
       <c r="A2503" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2503">
         <v>4.6</v>
@@ -33327,7 +33330,7 @@
     </row>
     <row r="2504" spans="1:9">
       <c r="A2504" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2504">
         <v>33.2</v>
@@ -33356,7 +33359,7 @@
     </row>
     <row r="2505" spans="1:9">
       <c r="A2505" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2505">
         <v>17.4</v>
